--- a/app/static/test_case_portfolio.xlsx
+++ b/app/static/test_case_portfolio.xlsx
@@ -5,19 +5,18 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joutoushou/development/autoTest/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joutoushou/development/flask/mathg/app/static/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE1F5B96-5BB4-5242-AAE1-88A050C3C352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3355C9D2-47D8-1849-8210-26F1B9237432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2440" yWindow="820" windowWidth="26340" windowHeight="18520" activeTab="1" xr2:uid="{934E95A7-77E6-E348-B224-445686B289E8}"/>
   </bookViews>
   <sheets>
     <sheet name="簡易仕様書" sheetId="1" r:id="rId1"/>
     <sheet name="テストケース" sheetId="5" r:id="rId2"/>
-    <sheet name="テスト報告" sheetId="4" r:id="rId3"/>
-    <sheet name="機能要件" sheetId="2" r:id="rId4"/>
-    <sheet name="非機能要件" sheetId="3" r:id="rId5"/>
+    <sheet name="機能要件" sheetId="2" r:id="rId3"/>
+    <sheet name="非機能要件" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">簡易仕様書!$F$27</definedName>
@@ -4598,6 +4597,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4616,23 +4630,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4646,42 +4645,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="26">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+          <bgColor theme="4" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4717,7 +4709,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4731,21 +4723,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+          <bgColor theme="4" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4761,27 +4739,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4822,15 +4779,22 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF8B9AC"/>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF0FE96"/>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4843,44 +4807,15 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-          <bgColor rgb="FF60EE64"/>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF8B9AC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+          <bgColor rgb="FFF0FE96"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5309,7 +5244,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
     </row>
@@ -5337,7 +5272,7 @@
       <c r="J2" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="K2" s="48">
+      <c r="K2" s="32">
         <f>K4/K3</f>
         <v>0.77472527472527475</v>
       </c>
@@ -5364,15 +5299,15 @@
       <c r="A5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
       <c r="J5" s="16" t="s">
         <v>322</v>
       </c>
@@ -5385,15 +5320,15 @@
       <c r="A6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
       <c r="J6" s="15" t="s">
         <v>323</v>
       </c>
@@ -5406,15 +5341,15 @@
       <c r="A7" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
       <c r="J7" s="17" t="s">
         <v>24</v>
       </c>
@@ -5427,15 +5362,15 @@
       <c r="A8" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="37" t="s">
         <v>360</v>
       </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
       <c r="J8" s="12" t="s">
         <v>25</v>
       </c>
@@ -5448,15 +5383,15 @@
       <c r="A9" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="39" t="s">
         <v>361</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="36"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="41"/>
       <c r="J9" s="1"/>
     </row>
     <row r="11" spans="1:11">
@@ -5468,81 +5403,81 @@
       <c r="A12" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33" t="s">
+      <c r="C12" s="38"/>
+      <c r="D12" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="32" t="s">
+      <c r="C13" s="36"/>
+      <c r="D13" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="32" t="s">
+      <c r="C14" s="36"/>
+      <c r="D14" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="32" t="s">
+      <c r="C15" s="36"/>
+      <c r="D15" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="32" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
     </row>
     <row r="17" spans="1:13">
       <c r="B17" s="7"/>
@@ -5649,15 +5584,15 @@
       <c r="C28" s="1"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37" t="s">
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="E29" s="37"/>
+      <c r="E29" s="35"/>
       <c r="F29" s="18" t="s">
         <v>209</v>
       </c>
@@ -5684,15 +5619,15 @@
       </c>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="38" t="s">
+      <c r="A30" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="B30" s="38"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38" t="s">
+      <c r="B30" s="33"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="E30" s="38"/>
+      <c r="E30" s="33"/>
       <c r="F30" s="1" t="s">
         <v>210</v>
       </c>
@@ -5722,16 +5657,16 @@
       </c>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="B31" s="38"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="38" t="str">
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33" t="str">
         <f>A31</f>
         <v>IMP</v>
       </c>
-      <c r="E31" s="38"/>
+      <c r="E31" s="33"/>
       <c r="F31" s="1" t="s">
         <v>211</v>
       </c>
@@ -5761,16 +5696,16 @@
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="38" t="s">
+      <c r="A32" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="B32" s="38"/>
-      <c r="C32" s="38"/>
-      <c r="D32" s="38" t="str">
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33" t="str">
         <f t="shared" ref="D32:D59" si="1">A32</f>
         <v>MIBG（腫瘍）</v>
       </c>
-      <c r="E32" s="38"/>
+      <c r="E32" s="33"/>
       <c r="F32" s="1" t="s">
         <v>212</v>
       </c>
@@ -5800,16 +5735,16 @@
       </c>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" s="38" t="s">
+      <c r="A33" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="B33" s="38"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="38" t="str">
+      <c r="B33" s="33"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33" t="str">
         <f t="shared" si="1"/>
         <v>MIBG（心筋）</v>
       </c>
-      <c r="E33" s="38"/>
+      <c r="E33" s="33"/>
       <c r="F33" s="1" t="s">
         <v>213</v>
       </c>
@@ -5837,16 +5772,16 @@
       </c>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="38" t="s">
+      <c r="A34" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38" t="str">
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33" t="str">
         <f t="shared" si="1"/>
         <v>イオマゼニル</v>
       </c>
-      <c r="E34" s="38"/>
+      <c r="E34" s="33"/>
       <c r="F34" s="1" t="s">
         <v>214</v>
       </c>
@@ -5874,16 +5809,16 @@
       </c>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" s="38" t="s">
+      <c r="A35" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38" t="str">
+      <c r="B35" s="33"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33" t="str">
         <f t="shared" si="1"/>
         <v>BMIPP</v>
       </c>
-      <c r="E35" s="38"/>
+      <c r="E35" s="33"/>
       <c r="F35" s="1" t="s">
         <v>215</v>
       </c>
@@ -5911,16 +5846,16 @@
       </c>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="38" t="s">
+      <c r="A36" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38" t="str">
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33" t="str">
         <f t="shared" si="1"/>
         <v>FDG（体幹）</v>
       </c>
-      <c r="E36" s="38"/>
+      <c r="E36" s="33"/>
       <c r="F36" s="1" t="s">
         <v>216</v>
       </c>
@@ -5948,16 +5883,16 @@
       </c>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" s="38" t="s">
+      <c r="A37" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38" t="str">
+      <c r="B37" s="33"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33" t="str">
         <f t="shared" si="1"/>
         <v>FDG（脳）</v>
       </c>
-      <c r="E37" s="38"/>
+      <c r="E37" s="33"/>
       <c r="F37" s="1" t="s">
         <v>217</v>
       </c>
@@ -5985,16 +5920,16 @@
       </c>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" s="38" t="s">
+      <c r="A38" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38" t="str">
+      <c r="B38" s="33"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33" t="str">
         <f t="shared" si="1"/>
         <v>クエン酸</v>
       </c>
-      <c r="E38" s="38"/>
+      <c r="E38" s="33"/>
       <c r="F38" s="1" t="s">
         <v>218</v>
       </c>
@@ -6022,16 +5957,16 @@
       </c>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" s="38" t="s">
+      <c r="A39" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="B39" s="38"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38" t="str">
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33" t="str">
         <f t="shared" si="1"/>
         <v>アルブミン（心プール）</v>
       </c>
-      <c r="E39" s="38"/>
+      <c r="E39" s="33"/>
       <c r="F39" s="1" t="s">
         <v>219</v>
       </c>
@@ -6059,16 +5994,16 @@
       </c>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="38" t="s">
+      <c r="A40" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="B40" s="38"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38" t="str">
+      <c r="B40" s="33"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33" t="str">
         <f t="shared" si="1"/>
         <v>スズコロイド（肝脾）</v>
       </c>
-      <c r="E40" s="38"/>
+      <c r="E40" s="33"/>
       <c r="F40" s="1" t="s">
         <v>220</v>
       </c>
@@ -6096,16 +6031,16 @@
       </c>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="38" t="s">
+      <c r="A41" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="B41" s="38"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="38" t="str">
+      <c r="B41" s="33"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33" t="str">
         <f t="shared" si="1"/>
         <v>スズコロイド（骨髄）</v>
       </c>
-      <c r="E41" s="38"/>
+      <c r="E41" s="33"/>
       <c r="F41" s="1" t="s">
         <v>221</v>
       </c>
@@ -6133,16 +6068,16 @@
       </c>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="38" t="s">
+      <c r="A42" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="B42" s="38"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38" t="str">
+      <c r="B42" s="33"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33" t="str">
         <f t="shared" si="1"/>
         <v>フィチン酸（肝脾）</v>
       </c>
-      <c r="E42" s="38"/>
+      <c r="E42" s="33"/>
       <c r="F42" s="1" t="s">
         <v>222</v>
       </c>
@@ -6170,15 +6105,15 @@
       </c>
     </row>
     <row r="43" spans="1:13">
-      <c r="A43" s="38" t="s">
+      <c r="A43" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38" t="s">
+      <c r="B43" s="33"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="E43" s="38"/>
+      <c r="E43" s="33"/>
       <c r="F43" s="1" t="s">
         <v>223</v>
       </c>
@@ -6206,16 +6141,16 @@
       </c>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="38" t="s">
+      <c r="A44" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="B44" s="38"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38" t="str">
+      <c r="B44" s="33"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="33" t="str">
         <f t="shared" si="1"/>
         <v>MDP/HMDP</v>
       </c>
-      <c r="E44" s="38"/>
+      <c r="E44" s="33"/>
       <c r="F44" s="1" t="s">
         <v>224</v>
       </c>
@@ -6243,16 +6178,16 @@
       </c>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="38" t="s">
+      <c r="A45" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="B45" s="38"/>
-      <c r="C45" s="38"/>
-      <c r="D45" s="38" t="str">
+      <c r="B45" s="33"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="33" t="str">
         <f t="shared" si="1"/>
         <v>DMSA</v>
       </c>
-      <c r="E45" s="38"/>
+      <c r="E45" s="33"/>
       <c r="F45" s="1" t="s">
         <v>225</v>
       </c>
@@ -6280,16 +6215,16 @@
       </c>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="38" t="s">
+      <c r="A46" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="B46" s="38"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38" t="str">
+      <c r="B46" s="33"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="33" t="str">
         <f t="shared" si="1"/>
         <v>DTPA</v>
       </c>
-      <c r="E46" s="38"/>
+      <c r="E46" s="33"/>
       <c r="F46" s="1" t="s">
         <v>226</v>
       </c>
@@ -6317,16 +6252,16 @@
       </c>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="38" t="s">
+      <c r="A47" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="B47" s="38"/>
-      <c r="C47" s="38"/>
-      <c r="D47" s="38" t="str">
+      <c r="B47" s="33"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="33" t="str">
         <f t="shared" si="1"/>
         <v>MAG3</v>
       </c>
-      <c r="E47" s="38"/>
+      <c r="E47" s="33"/>
       <c r="F47" s="1" t="s">
         <v>227</v>
       </c>
@@ -6354,16 +6289,16 @@
       </c>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="38" t="s">
+      <c r="A48" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="B48" s="38"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="38" t="str">
+      <c r="B48" s="33"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="33" t="str">
         <f t="shared" si="1"/>
         <v>ECD</v>
       </c>
-      <c r="E48" s="38"/>
+      <c r="E48" s="33"/>
       <c r="F48" s="1" t="s">
         <v>228</v>
       </c>
@@ -6391,16 +6326,16 @@
       </c>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="38" t="s">
+      <c r="A49" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="B49" s="38"/>
-      <c r="C49" s="38"/>
-      <c r="D49" s="38" t="str">
+      <c r="B49" s="33"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="33" t="str">
         <f t="shared" si="1"/>
         <v>HMPAO</v>
       </c>
-      <c r="E49" s="38"/>
+      <c r="E49" s="33"/>
       <c r="F49" s="1" t="s">
         <v>229</v>
       </c>
@@ -6430,16 +6365,16 @@
       </c>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="38" t="s">
+      <c r="A50" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="B50" s="38"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38" t="str">
+      <c r="B50" s="33"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="33" t="str">
         <f t="shared" si="1"/>
         <v>PMT</v>
       </c>
-      <c r="E50" s="38"/>
+      <c r="E50" s="33"/>
       <c r="F50" s="1" t="s">
         <v>230</v>
       </c>
@@ -6467,16 +6402,16 @@
       </c>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="38" t="s">
+      <c r="A51" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="B51" s="38"/>
-      <c r="C51" s="38"/>
-      <c r="D51" s="38" t="str">
+      <c r="B51" s="33"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="33" t="str">
         <f t="shared" si="1"/>
         <v>MAA</v>
       </c>
-      <c r="E51" s="38"/>
+      <c r="E51" s="33"/>
       <c r="F51" s="1" t="s">
         <v>231</v>
       </c>
@@ -6504,15 +6439,15 @@
       </c>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="38" t="s">
+      <c r="A52" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="B52" s="38"/>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38" t="s">
+      <c r="B52" s="33"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="E52" s="38"/>
+      <c r="E52" s="33"/>
       <c r="F52" s="1" t="s">
         <v>232</v>
       </c>
@@ -6540,15 +6475,15 @@
       </c>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="38" t="s">
+      <c r="A53" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="B53" s="38"/>
-      <c r="C53" s="38"/>
-      <c r="D53" s="38" t="s">
+      <c r="B53" s="33"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="E53" s="38"/>
+      <c r="E53" s="33"/>
       <c r="F53" s="1" t="s">
         <v>233</v>
       </c>
@@ -6576,16 +6511,16 @@
       </c>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="38" t="s">
+      <c r="A54" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="B54" s="38"/>
-      <c r="C54" s="38"/>
-      <c r="D54" s="38" t="str">
+      <c r="B54" s="33"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="33" t="str">
         <f t="shared" si="1"/>
         <v>RBC</v>
       </c>
-      <c r="E54" s="38"/>
+      <c r="E54" s="33"/>
       <c r="F54" s="1" t="s">
         <v>234</v>
       </c>
@@ -6613,15 +6548,15 @@
       </c>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="38" t="s">
+      <c r="A55" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="B55" s="38"/>
-      <c r="C55" s="38"/>
-      <c r="D55" s="38" t="s">
+      <c r="B55" s="33"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E55" s="38"/>
+      <c r="E55" s="33"/>
       <c r="F55" s="1" t="s">
         <v>235</v>
       </c>
@@ -6649,15 +6584,15 @@
       </c>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="39" t="s">
+      <c r="A56" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="B56" s="39"/>
-      <c r="C56" s="39"/>
-      <c r="D56" s="38" t="s">
+      <c r="B56" s="34"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="33" t="s">
         <v>191</v>
       </c>
-      <c r="E56" s="38"/>
+      <c r="E56" s="33"/>
       <c r="F56" s="1" t="s">
         <v>236</v>
       </c>
@@ -6685,15 +6620,15 @@
       </c>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="39" t="s">
+      <c r="A57" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="B57" s="39"/>
-      <c r="C57" s="39"/>
-      <c r="D57" s="38" t="s">
+      <c r="B57" s="34"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="E57" s="38"/>
+      <c r="E57" s="33"/>
       <c r="F57" s="1" t="s">
         <v>237</v>
       </c>
@@ -6721,15 +6656,15 @@
       </c>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="39" t="s">
+      <c r="A58" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="B58" s="39"/>
-      <c r="C58" s="39"/>
-      <c r="D58" s="38" t="s">
+      <c r="B58" s="34"/>
+      <c r="C58" s="34"/>
+      <c r="D58" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="E58" s="38"/>
+      <c r="E58" s="33"/>
       <c r="F58" s="1" t="s">
         <v>238</v>
       </c>
@@ -6757,16 +6692,16 @@
       </c>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="38" t="s">
+      <c r="A59" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="B59" s="38"/>
-      <c r="C59" s="38"/>
-      <c r="D59" s="38" t="str">
+      <c r="B59" s="33"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="33" t="str">
         <f t="shared" si="1"/>
         <v>GSA</v>
       </c>
-      <c r="E59" s="38"/>
+      <c r="E59" s="33"/>
       <c r="F59" s="1" t="s">
         <v>239</v>
       </c>
@@ -6796,15 +6731,15 @@
       </c>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="38" t="s">
+      <c r="A60" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="B60" s="38"/>
-      <c r="C60" s="38"/>
-      <c r="D60" s="38" t="s">
+      <c r="B60" s="33"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="E60" s="38"/>
+      <c r="E60" s="33"/>
       <c r="F60" s="1" t="s">
         <v>240</v>
       </c>
@@ -6832,15 +6767,15 @@
       </c>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="38" t="s">
+      <c r="A61" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="B61" s="38"/>
-      <c r="C61" s="38"/>
-      <c r="D61" s="38" t="s">
+      <c r="B61" s="33"/>
+      <c r="C61" s="33"/>
+      <c r="D61" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="E61" s="38"/>
+      <c r="E61" s="33"/>
       <c r="F61" s="1" t="s">
         <v>241</v>
       </c>
@@ -7028,13 +6963,64 @@
     </row>
   </sheetData>
   <mergeCells count="81">
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="D42:E42"/>
     <mergeCell ref="D41:E41"/>
@@ -7051,74 +7037,23 @@
     <mergeCell ref="D52:E52"/>
     <mergeCell ref="D53:E53"/>
     <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D59:E59"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="J5:J7">
-    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="保留">
+    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="保留">
       <formula>NOT(ISERROR(SEARCH("保留",J5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="2" operator="containsText" text="NG">
+    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="NG">
       <formula>NOT(ISERROR(SEARCH("NG",J5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",J5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7153,45 +7088,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>262</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="40" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="42" t="s">
         <v>264</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
       <c r="F1" s="1"/>
       <c r="G1" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="42" t="s">
         <v>367</v>
       </c>
-      <c r="I1" s="40"/>
+      <c r="I1" s="42"/>
       <c r="J1" s="12" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:29">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="38" t="s">
         <v>263</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="40" t="s">
+      <c r="B2" s="38"/>
+      <c r="C2" s="42" t="s">
         <v>265</v>
       </c>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
       <c r="F2" s="1"/>
       <c r="G2" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="42" t="s">
         <v>368</v>
       </c>
-      <c r="I2" s="40"/>
+      <c r="I2" s="42"/>
       <c r="J2" s="14" t="s">
         <v>356</v>
       </c>
@@ -7289,10 +7224,10 @@
       <c r="C4" s="46" t="s">
         <v>324</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="42" t="s">
         <v>145</v>
       </c>
       <c r="F4" s="14" t="s">
@@ -7373,8 +7308,8 @@
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="46"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
       <c r="F5" s="14" t="s">
         <v>267</v>
       </c>
@@ -7456,8 +7391,8 @@
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
       <c r="F6" s="14" t="s">
         <v>267</v>
       </c>
@@ -7536,8 +7471,8 @@
       </c>
       <c r="B7" s="44"/>
       <c r="C7" s="46"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
       <c r="F7" s="14" t="s">
         <v>267</v>
       </c>
@@ -7618,8 +7553,8 @@
       </c>
       <c r="B8" s="44"/>
       <c r="C8" s="46"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
       <c r="F8" s="14" t="s">
         <v>267</v>
       </c>
@@ -7698,8 +7633,8 @@
       </c>
       <c r="B9" s="44"/>
       <c r="C9" s="46"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
       <c r="F9" s="14" t="s">
         <v>267</v>
       </c>
@@ -7777,8 +7712,8 @@
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="46"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
       <c r="F10" s="14" t="s">
         <v>267</v>
       </c>
@@ -7855,8 +7790,8 @@
       </c>
       <c r="B11" s="44"/>
       <c r="C11" s="46"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
       <c r="F11" s="14" t="s">
         <v>267</v>
       </c>
@@ -7935,8 +7870,8 @@
       </c>
       <c r="B12" s="44"/>
       <c r="C12" s="46"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
       <c r="F12" s="14" t="s">
         <v>267</v>
       </c>
@@ -8013,8 +7948,8 @@
       </c>
       <c r="B13" s="44"/>
       <c r="C13" s="46"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
       <c r="F13" s="14" t="s">
         <v>267</v>
       </c>
@@ -8093,8 +8028,8 @@
       </c>
       <c r="B14" s="44"/>
       <c r="C14" s="46"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
       <c r="F14" s="14" t="s">
         <v>267</v>
       </c>
@@ -8173,8 +8108,8 @@
       </c>
       <c r="B15" s="44"/>
       <c r="C15" s="46"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
       <c r="F15" s="14" t="s">
         <v>267</v>
       </c>
@@ -8253,8 +8188,8 @@
       </c>
       <c r="B16" s="44"/>
       <c r="C16" s="46"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
       <c r="F16" s="14" t="s">
         <v>267</v>
       </c>
@@ -8332,8 +8267,8 @@
       </c>
       <c r="B17" s="44"/>
       <c r="C17" s="46"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
       <c r="F17" s="14" t="s">
         <v>267</v>
       </c>
@@ -8410,8 +8345,8 @@
       </c>
       <c r="B18" s="44"/>
       <c r="C18" s="46"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
       <c r="F18" s="14" t="s">
         <v>267</v>
       </c>
@@ -8490,8 +8425,8 @@
       </c>
       <c r="B19" s="44"/>
       <c r="C19" s="46"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
       <c r="F19" s="14" t="s">
         <v>267</v>
       </c>
@@ -8570,8 +8505,8 @@
       </c>
       <c r="B20" s="44"/>
       <c r="C20" s="46"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
       <c r="F20" s="14" t="s">
         <v>267</v>
       </c>
@@ -8651,8 +8586,8 @@
       </c>
       <c r="B21" s="44"/>
       <c r="C21" s="46"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
       <c r="F21" s="14" t="s">
         <v>267</v>
       </c>
@@ -8729,8 +8664,8 @@
       </c>
       <c r="B22" s="44"/>
       <c r="C22" s="46"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
       <c r="F22" s="14" t="s">
         <v>267</v>
       </c>
@@ -8809,8 +8744,8 @@
       </c>
       <c r="B23" s="44"/>
       <c r="C23" s="46"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
       <c r="F23" s="14" t="s">
         <v>267</v>
       </c>
@@ -8889,8 +8824,8 @@
       </c>
       <c r="B24" s="44"/>
       <c r="C24" s="46"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
       <c r="F24" s="14" t="s">
         <v>267</v>
       </c>
@@ -8968,8 +8903,8 @@
       </c>
       <c r="B25" s="44"/>
       <c r="C25" s="46"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
       <c r="F25" s="14" t="s">
         <v>267</v>
       </c>
@@ -9046,8 +8981,8 @@
       </c>
       <c r="B26" s="44"/>
       <c r="C26" s="46"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
       <c r="F26" s="14" t="s">
         <v>267</v>
       </c>
@@ -9126,8 +9061,8 @@
       </c>
       <c r="B27" s="44"/>
       <c r="C27" s="46"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
       <c r="F27" s="14" t="s">
         <v>267</v>
       </c>
@@ -9206,8 +9141,8 @@
       </c>
       <c r="B28" s="44"/>
       <c r="C28" s="46"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
       <c r="F28" s="14" t="s">
         <v>267</v>
       </c>
@@ -9285,8 +9220,8 @@
       </c>
       <c r="B29" s="44"/>
       <c r="C29" s="46"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
       <c r="F29" s="14" t="s">
         <v>267</v>
       </c>
@@ -9365,8 +9300,8 @@
       </c>
       <c r="B30" s="44"/>
       <c r="C30" s="46"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
       <c r="F30" s="14" t="s">
         <v>267</v>
       </c>
@@ -9445,8 +9380,8 @@
       </c>
       <c r="B31" s="44"/>
       <c r="C31" s="46"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
       <c r="F31" s="14" t="s">
         <v>267</v>
       </c>
@@ -9525,8 +9460,8 @@
       </c>
       <c r="B32" s="44"/>
       <c r="C32" s="46"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
       <c r="F32" s="14" t="s">
         <v>267</v>
       </c>
@@ -9604,8 +9539,8 @@
       </c>
       <c r="B33" s="44"/>
       <c r="C33" s="46"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
       <c r="F33" s="14" t="s">
         <v>267</v>
       </c>
@@ -9682,8 +9617,8 @@
       </c>
       <c r="B34" s="44"/>
       <c r="C34" s="46"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
       <c r="F34" s="14" t="s">
         <v>267</v>
       </c>
@@ -9762,8 +9697,8 @@
       </c>
       <c r="B35" s="44"/>
       <c r="C35" s="46"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
       <c r="F35" s="14" t="s">
         <v>267</v>
       </c>
@@ -9842,8 +9777,8 @@
       </c>
       <c r="B36" s="44"/>
       <c r="C36" s="46"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42"/>
       <c r="F36" s="14" t="s">
         <v>267</v>
       </c>
@@ -9921,8 +9856,8 @@
       </c>
       <c r="B37" s="44"/>
       <c r="C37" s="46"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42"/>
       <c r="F37" s="14" t="s">
         <v>267</v>
       </c>
@@ -9999,8 +9934,8 @@
       </c>
       <c r="B38" s="44"/>
       <c r="C38" s="46"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
       <c r="F38" s="14" t="s">
         <v>267</v>
       </c>
@@ -10079,8 +10014,8 @@
       </c>
       <c r="B39" s="44"/>
       <c r="C39" s="46"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="40"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
       <c r="F39" s="14" t="s">
         <v>267</v>
       </c>
@@ -10159,8 +10094,8 @@
       </c>
       <c r="B40" s="44"/>
       <c r="C40" s="46"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="40"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
       <c r="F40" s="14" t="s">
         <v>267</v>
       </c>
@@ -10238,8 +10173,8 @@
       </c>
       <c r="B41" s="44"/>
       <c r="C41" s="46"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
       <c r="F41" s="14" t="s">
         <v>267</v>
       </c>
@@ -10318,8 +10253,8 @@
       </c>
       <c r="B42" s="44"/>
       <c r="C42" s="46"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="40"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
       <c r="F42" s="14" t="s">
         <v>267</v>
       </c>
@@ -10398,8 +10333,8 @@
       </c>
       <c r="B43" s="44"/>
       <c r="C43" s="46"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="42"/>
       <c r="F43" s="14" t="s">
         <v>267</v>
       </c>
@@ -10480,8 +10415,8 @@
       </c>
       <c r="B44" s="44"/>
       <c r="C44" s="46"/>
-      <c r="D44" s="40"/>
-      <c r="E44" s="40"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="42"/>
       <c r="F44" s="14" t="s">
         <v>267</v>
       </c>
@@ -10561,8 +10496,8 @@
       </c>
       <c r="B45" s="44"/>
       <c r="C45" s="46"/>
-      <c r="D45" s="40"/>
-      <c r="E45" s="40"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
       <c r="F45" s="14" t="s">
         <v>267</v>
       </c>
@@ -10639,8 +10574,8 @@
       </c>
       <c r="B46" s="44"/>
       <c r="C46" s="46"/>
-      <c r="D46" s="40"/>
-      <c r="E46" s="40"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="42"/>
       <c r="F46" s="14" t="s">
         <v>267</v>
       </c>
@@ -10719,8 +10654,8 @@
       </c>
       <c r="B47" s="44"/>
       <c r="C47" s="46"/>
-      <c r="D47" s="40"/>
-      <c r="E47" s="40"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
       <c r="F47" s="14" t="s">
         <v>267</v>
       </c>
@@ -10799,8 +10734,8 @@
       </c>
       <c r="B48" s="44"/>
       <c r="C48" s="46"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="40"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
       <c r="F48" s="14" t="s">
         <v>267</v>
       </c>
@@ -10878,8 +10813,8 @@
       </c>
       <c r="B49" s="44"/>
       <c r="C49" s="46"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
       <c r="F49" s="14" t="s">
         <v>267</v>
       </c>
@@ -10956,8 +10891,8 @@
       </c>
       <c r="B50" s="44"/>
       <c r="C50" s="46"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
       <c r="F50" s="14" t="s">
         <v>267</v>
       </c>
@@ -11036,8 +10971,8 @@
       </c>
       <c r="B51" s="44"/>
       <c r="C51" s="46"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
       <c r="F51" s="14" t="s">
         <v>267</v>
       </c>
@@ -11116,8 +11051,8 @@
       </c>
       <c r="B52" s="44"/>
       <c r="C52" s="46"/>
-      <c r="D52" s="40"/>
-      <c r="E52" s="40"/>
+      <c r="D52" s="42"/>
+      <c r="E52" s="42"/>
       <c r="F52" s="14" t="s">
         <v>267</v>
       </c>
@@ -11195,8 +11130,8 @@
       </c>
       <c r="B53" s="44"/>
       <c r="C53" s="46"/>
-      <c r="D53" s="40"/>
-      <c r="E53" s="40"/>
+      <c r="D53" s="42"/>
+      <c r="E53" s="42"/>
       <c r="F53" s="14" t="s">
         <v>267</v>
       </c>
@@ -11273,8 +11208,8 @@
       </c>
       <c r="B54" s="44"/>
       <c r="C54" s="46"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="42"/>
       <c r="F54" s="14" t="s">
         <v>267</v>
       </c>
@@ -11353,8 +11288,8 @@
       </c>
       <c r="B55" s="44"/>
       <c r="C55" s="46"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="40"/>
+      <c r="D55" s="42"/>
+      <c r="E55" s="42"/>
       <c r="F55" s="14" t="s">
         <v>267</v>
       </c>
@@ -11435,8 +11370,8 @@
       </c>
       <c r="B56" s="44"/>
       <c r="C56" s="46"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="40"/>
+      <c r="D56" s="42"/>
+      <c r="E56" s="42"/>
       <c r="F56" s="14" t="s">
         <v>267</v>
       </c>
@@ -11514,8 +11449,8 @@
       </c>
       <c r="B57" s="44"/>
       <c r="C57" s="46"/>
-      <c r="D57" s="40"/>
-      <c r="E57" s="40"/>
+      <c r="D57" s="42"/>
+      <c r="E57" s="42"/>
       <c r="F57" s="14" t="s">
         <v>267</v>
       </c>
@@ -11592,8 +11527,8 @@
       </c>
       <c r="B58" s="44"/>
       <c r="C58" s="46"/>
-      <c r="D58" s="40"/>
-      <c r="E58" s="40"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="42"/>
       <c r="F58" s="14" t="s">
         <v>267</v>
       </c>
@@ -11672,8 +11607,8 @@
       </c>
       <c r="B59" s="44"/>
       <c r="C59" s="46"/>
-      <c r="D59" s="40"/>
-      <c r="E59" s="40"/>
+      <c r="D59" s="42"/>
+      <c r="E59" s="42"/>
       <c r="F59" s="14" t="s">
         <v>267</v>
       </c>
@@ -11752,8 +11687,8 @@
       </c>
       <c r="B60" s="44"/>
       <c r="C60" s="46"/>
-      <c r="D60" s="40"/>
-      <c r="E60" s="40"/>
+      <c r="D60" s="42"/>
+      <c r="E60" s="42"/>
       <c r="F60" s="14" t="s">
         <v>267</v>
       </c>
@@ -11831,8 +11766,8 @@
       </c>
       <c r="B61" s="44"/>
       <c r="C61" s="46"/>
-      <c r="D61" s="40"/>
-      <c r="E61" s="40"/>
+      <c r="D61" s="42"/>
+      <c r="E61" s="42"/>
       <c r="F61" s="14" t="s">
         <v>267</v>
       </c>
@@ -11911,8 +11846,8 @@
       </c>
       <c r="B62" s="44"/>
       <c r="C62" s="46"/>
-      <c r="D62" s="40"/>
-      <c r="E62" s="40"/>
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
       <c r="F62" s="14" t="s">
         <v>267</v>
       </c>
@@ -11991,8 +11926,8 @@
       </c>
       <c r="B63" s="44"/>
       <c r="C63" s="46"/>
-      <c r="D63" s="40"/>
-      <c r="E63" s="40"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="42"/>
       <c r="F63" s="14" t="s">
         <v>267</v>
       </c>
@@ -12073,8 +12008,8 @@
       </c>
       <c r="B64" s="44"/>
       <c r="C64" s="46"/>
-      <c r="D64" s="40"/>
-      <c r="E64" s="40"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="42"/>
       <c r="F64" s="14" t="s">
         <v>267</v>
       </c>
@@ -12152,8 +12087,8 @@
       </c>
       <c r="B65" s="44"/>
       <c r="C65" s="46"/>
-      <c r="D65" s="40"/>
-      <c r="E65" s="40"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="42"/>
       <c r="F65" s="14" t="s">
         <v>267</v>
       </c>
@@ -12230,8 +12165,8 @@
       </c>
       <c r="B66" s="44"/>
       <c r="C66" s="46"/>
-      <c r="D66" s="40"/>
-      <c r="E66" s="40"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
       <c r="F66" s="14" t="s">
         <v>267</v>
       </c>
@@ -12310,8 +12245,8 @@
       </c>
       <c r="B67" s="44"/>
       <c r="C67" s="46"/>
-      <c r="D67" s="40"/>
-      <c r="E67" s="40"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
       <c r="F67" s="14" t="s">
         <v>267</v>
       </c>
@@ -12390,8 +12325,8 @@
       </c>
       <c r="B68" s="44"/>
       <c r="C68" s="46"/>
-      <c r="D68" s="40"/>
-      <c r="E68" s="40"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="42"/>
       <c r="F68" s="14" t="s">
         <v>267</v>
       </c>
@@ -12469,8 +12404,8 @@
       </c>
       <c r="B69" s="44"/>
       <c r="C69" s="46"/>
-      <c r="D69" s="40"/>
-      <c r="E69" s="40"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
       <c r="F69" s="14" t="s">
         <v>267</v>
       </c>
@@ -12547,8 +12482,8 @@
       </c>
       <c r="B70" s="44"/>
       <c r="C70" s="46"/>
-      <c r="D70" s="40"/>
-      <c r="E70" s="40"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
       <c r="F70" s="14" t="s">
         <v>267</v>
       </c>
@@ -12627,8 +12562,8 @@
       </c>
       <c r="B71" s="44"/>
       <c r="C71" s="46"/>
-      <c r="D71" s="40"/>
-      <c r="E71" s="40"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="42"/>
       <c r="F71" s="14" t="s">
         <v>267</v>
       </c>
@@ -12707,8 +12642,8 @@
       </c>
       <c r="B72" s="44"/>
       <c r="C72" s="46"/>
-      <c r="D72" s="40"/>
-      <c r="E72" s="40"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
       <c r="F72" s="14" t="s">
         <v>267</v>
       </c>
@@ -12786,8 +12721,8 @@
       </c>
       <c r="B73" s="44"/>
       <c r="C73" s="46"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="40"/>
+      <c r="D73" s="42"/>
+      <c r="E73" s="42"/>
       <c r="F73" s="14" t="s">
         <v>267</v>
       </c>
@@ -12866,8 +12801,8 @@
       </c>
       <c r="B74" s="44"/>
       <c r="C74" s="46"/>
-      <c r="D74" s="40"/>
-      <c r="E74" s="40"/>
+      <c r="D74" s="42"/>
+      <c r="E74" s="42"/>
       <c r="F74" s="14" t="s">
         <v>267</v>
       </c>
@@ -12946,8 +12881,8 @@
       </c>
       <c r="B75" s="44"/>
       <c r="C75" s="46"/>
-      <c r="D75" s="40"/>
-      <c r="E75" s="40"/>
+      <c r="D75" s="42"/>
+      <c r="E75" s="42"/>
       <c r="F75" s="14" t="s">
         <v>267</v>
       </c>
@@ -13026,8 +12961,8 @@
       </c>
       <c r="B76" s="44"/>
       <c r="C76" s="46"/>
-      <c r="D76" s="40"/>
-      <c r="E76" s="40"/>
+      <c r="D76" s="42"/>
+      <c r="E76" s="42"/>
       <c r="F76" s="14" t="s">
         <v>267</v>
       </c>
@@ -13105,8 +13040,8 @@
       </c>
       <c r="B77" s="44"/>
       <c r="C77" s="46"/>
-      <c r="D77" s="40"/>
-      <c r="E77" s="40"/>
+      <c r="D77" s="42"/>
+      <c r="E77" s="42"/>
       <c r="F77" s="14" t="s">
         <v>267</v>
       </c>
@@ -13183,8 +13118,8 @@
       </c>
       <c r="B78" s="44"/>
       <c r="C78" s="46"/>
-      <c r="D78" s="40"/>
-      <c r="E78" s="40"/>
+      <c r="D78" s="42"/>
+      <c r="E78" s="42"/>
       <c r="F78" s="14" t="s">
         <v>267</v>
       </c>
@@ -13263,8 +13198,8 @@
       </c>
       <c r="B79" s="44"/>
       <c r="C79" s="46"/>
-      <c r="D79" s="40"/>
-      <c r="E79" s="40"/>
+      <c r="D79" s="42"/>
+      <c r="E79" s="42"/>
       <c r="F79" s="14" t="s">
         <v>267</v>
       </c>
@@ -13341,8 +13276,8 @@
       </c>
       <c r="B80" s="44"/>
       <c r="C80" s="46"/>
-      <c r="D80" s="40"/>
-      <c r="E80" s="40"/>
+      <c r="D80" s="42"/>
+      <c r="E80" s="42"/>
       <c r="F80" s="14" t="s">
         <v>267</v>
       </c>
@@ -13421,8 +13356,8 @@
       </c>
       <c r="B81" s="44"/>
       <c r="C81" s="46"/>
-      <c r="D81" s="40"/>
-      <c r="E81" s="40"/>
+      <c r="D81" s="42"/>
+      <c r="E81" s="42"/>
       <c r="F81" s="14" t="s">
         <v>267</v>
       </c>
@@ -13499,8 +13434,8 @@
       </c>
       <c r="B82" s="44"/>
       <c r="C82" s="46"/>
-      <c r="D82" s="40"/>
-      <c r="E82" s="40"/>
+      <c r="D82" s="42"/>
+      <c r="E82" s="42"/>
       <c r="F82" s="14" t="s">
         <v>267</v>
       </c>
@@ -13577,8 +13512,8 @@
       </c>
       <c r="B83" s="44"/>
       <c r="C83" s="46"/>
-      <c r="D83" s="40"/>
-      <c r="E83" s="40"/>
+      <c r="D83" s="42"/>
+      <c r="E83" s="42"/>
       <c r="F83" s="14" t="s">
         <v>267</v>
       </c>
@@ -13657,8 +13592,8 @@
       </c>
       <c r="B84" s="44"/>
       <c r="C84" s="46"/>
-      <c r="D84" s="40"/>
-      <c r="E84" s="40"/>
+      <c r="D84" s="42"/>
+      <c r="E84" s="42"/>
       <c r="F84" s="14" t="s">
         <v>267</v>
       </c>
@@ -13739,8 +13674,8 @@
       </c>
       <c r="B85" s="44"/>
       <c r="C85" s="46"/>
-      <c r="D85" s="40"/>
-      <c r="E85" s="40"/>
+      <c r="D85" s="42"/>
+      <c r="E85" s="42"/>
       <c r="F85" s="14" t="s">
         <v>267</v>
       </c>
@@ -13820,8 +13755,8 @@
       </c>
       <c r="B86" s="44"/>
       <c r="C86" s="46"/>
-      <c r="D86" s="40"/>
-      <c r="E86" s="40"/>
+      <c r="D86" s="42"/>
+      <c r="E86" s="42"/>
       <c r="F86" s="14" t="s">
         <v>267</v>
       </c>
@@ -13898,8 +13833,8 @@
       </c>
       <c r="B87" s="44"/>
       <c r="C87" s="46"/>
-      <c r="D87" s="40"/>
-      <c r="E87" s="40"/>
+      <c r="D87" s="42"/>
+      <c r="E87" s="42"/>
       <c r="F87" s="14" t="s">
         <v>267</v>
       </c>
@@ -13978,8 +13913,8 @@
       </c>
       <c r="B88" s="44"/>
       <c r="C88" s="46"/>
-      <c r="D88" s="40"/>
-      <c r="E88" s="40"/>
+      <c r="D88" s="42"/>
+      <c r="E88" s="42"/>
       <c r="F88" s="14" t="s">
         <v>267</v>
       </c>
@@ -14058,8 +13993,8 @@
       </c>
       <c r="B89" s="44"/>
       <c r="C89" s="46"/>
-      <c r="D89" s="40"/>
-      <c r="E89" s="40"/>
+      <c r="D89" s="42"/>
+      <c r="E89" s="42"/>
       <c r="F89" s="14" t="s">
         <v>267</v>
       </c>
@@ -14136,8 +14071,8 @@
       </c>
       <c r="B90" s="44"/>
       <c r="C90" s="46"/>
-      <c r="D90" s="40"/>
-      <c r="E90" s="40"/>
+      <c r="D90" s="42"/>
+      <c r="E90" s="42"/>
       <c r="F90" s="14" t="s">
         <v>267</v>
       </c>
@@ -14216,8 +14151,8 @@
       </c>
       <c r="B91" s="44"/>
       <c r="C91" s="46"/>
-      <c r="D91" s="40"/>
-      <c r="E91" s="40"/>
+      <c r="D91" s="42"/>
+      <c r="E91" s="42"/>
       <c r="F91" s="14" t="s">
         <v>267</v>
       </c>
@@ -14296,8 +14231,8 @@
       </c>
       <c r="B92" s="44"/>
       <c r="C92" s="46"/>
-      <c r="D92" s="40"/>
-      <c r="E92" s="40"/>
+      <c r="D92" s="42"/>
+      <c r="E92" s="42"/>
       <c r="F92" s="14" t="s">
         <v>267</v>
       </c>
@@ -14375,8 +14310,8 @@
       </c>
       <c r="B93" s="44"/>
       <c r="C93" s="46"/>
-      <c r="D93" s="40"/>
-      <c r="E93" s="40"/>
+      <c r="D93" s="42"/>
+      <c r="E93" s="42"/>
       <c r="F93" s="14" t="s">
         <v>267</v>
       </c>
@@ -14453,8 +14388,8 @@
       </c>
       <c r="B94" s="44"/>
       <c r="C94" s="46"/>
-      <c r="D94" s="40"/>
-      <c r="E94" s="40"/>
+      <c r="D94" s="42"/>
+      <c r="E94" s="42"/>
       <c r="F94" s="14" t="s">
         <v>267</v>
       </c>
@@ -14533,8 +14468,8 @@
       </c>
       <c r="B95" s="44"/>
       <c r="C95" s="46"/>
-      <c r="D95" s="40"/>
-      <c r="E95" s="40"/>
+      <c r="D95" s="42"/>
+      <c r="E95" s="42"/>
       <c r="F95" s="14" t="s">
         <v>267</v>
       </c>
@@ -14613,8 +14548,8 @@
       </c>
       <c r="B96" s="44"/>
       <c r="C96" s="46"/>
-      <c r="D96" s="40"/>
-      <c r="E96" s="40"/>
+      <c r="D96" s="42"/>
+      <c r="E96" s="42"/>
       <c r="F96" s="14" t="s">
         <v>267</v>
       </c>
@@ -14692,8 +14627,8 @@
       </c>
       <c r="B97" s="44"/>
       <c r="C97" s="46"/>
-      <c r="D97" s="40"/>
-      <c r="E97" s="40"/>
+      <c r="D97" s="42"/>
+      <c r="E97" s="42"/>
       <c r="F97" s="14" t="s">
         <v>267</v>
       </c>
@@ -14770,8 +14705,8 @@
       </c>
       <c r="B98" s="44"/>
       <c r="C98" s="46"/>
-      <c r="D98" s="40"/>
-      <c r="E98" s="40"/>
+      <c r="D98" s="42"/>
+      <c r="E98" s="42"/>
       <c r="F98" s="14" t="s">
         <v>267</v>
       </c>
@@ -14850,8 +14785,8 @@
       </c>
       <c r="B99" s="44"/>
       <c r="C99" s="46"/>
-      <c r="D99" s="40"/>
-      <c r="E99" s="40"/>
+      <c r="D99" s="42"/>
+      <c r="E99" s="42"/>
       <c r="F99" s="14" t="s">
         <v>267</v>
       </c>
@@ -14932,8 +14867,8 @@
       </c>
       <c r="B100" s="44"/>
       <c r="C100" s="46"/>
-      <c r="D100" s="40"/>
-      <c r="E100" s="40"/>
+      <c r="D100" s="42"/>
+      <c r="E100" s="42"/>
       <c r="F100" s="14" t="s">
         <v>267</v>
       </c>
@@ -15011,8 +14946,8 @@
       </c>
       <c r="B101" s="44"/>
       <c r="C101" s="46"/>
-      <c r="D101" s="40"/>
-      <c r="E101" s="40"/>
+      <c r="D101" s="42"/>
+      <c r="E101" s="42"/>
       <c r="F101" s="14" t="s">
         <v>267</v>
       </c>
@@ -15089,8 +15024,8 @@
       </c>
       <c r="B102" s="44"/>
       <c r="C102" s="46"/>
-      <c r="D102" s="40"/>
-      <c r="E102" s="40"/>
+      <c r="D102" s="42"/>
+      <c r="E102" s="42"/>
       <c r="F102" s="14" t="s">
         <v>267</v>
       </c>
@@ -15169,8 +15104,8 @@
       </c>
       <c r="B103" s="44"/>
       <c r="C103" s="46"/>
-      <c r="D103" s="40"/>
-      <c r="E103" s="40"/>
+      <c r="D103" s="42"/>
+      <c r="E103" s="42"/>
       <c r="F103" s="14" t="s">
         <v>267</v>
       </c>
@@ -15249,8 +15184,8 @@
       </c>
       <c r="B104" s="44"/>
       <c r="C104" s="46"/>
-      <c r="D104" s="40"/>
-      <c r="E104" s="40"/>
+      <c r="D104" s="42"/>
+      <c r="E104" s="42"/>
       <c r="F104" s="14" t="s">
         <v>267</v>
       </c>
@@ -15330,8 +15265,8 @@
       </c>
       <c r="B105" s="44"/>
       <c r="C105" s="46"/>
-      <c r="D105" s="40"/>
-      <c r="E105" s="40"/>
+      <c r="D105" s="42"/>
+      <c r="E105" s="42"/>
       <c r="F105" s="14" t="s">
         <v>267</v>
       </c>
@@ -15410,8 +15345,8 @@
       </c>
       <c r="B106" s="44"/>
       <c r="C106" s="46"/>
-      <c r="D106" s="40"/>
-      <c r="E106" s="40"/>
+      <c r="D106" s="42"/>
+      <c r="E106" s="42"/>
       <c r="F106" s="14" t="s">
         <v>267</v>
       </c>
@@ -15490,8 +15425,8 @@
       </c>
       <c r="B107" s="44"/>
       <c r="C107" s="46"/>
-      <c r="D107" s="40"/>
-      <c r="E107" s="40"/>
+      <c r="D107" s="42"/>
+      <c r="E107" s="42"/>
       <c r="F107" s="14" t="s">
         <v>267</v>
       </c>
@@ -15570,8 +15505,8 @@
       </c>
       <c r="B108" s="44"/>
       <c r="C108" s="46"/>
-      <c r="D108" s="40"/>
-      <c r="E108" s="40"/>
+      <c r="D108" s="42"/>
+      <c r="E108" s="42"/>
       <c r="F108" s="14" t="s">
         <v>267</v>
       </c>
@@ -15649,8 +15584,8 @@
       </c>
       <c r="B109" s="44"/>
       <c r="C109" s="46"/>
-      <c r="D109" s="40"/>
-      <c r="E109" s="40"/>
+      <c r="D109" s="42"/>
+      <c r="E109" s="42"/>
       <c r="F109" s="14" t="s">
         <v>267</v>
       </c>
@@ -15727,8 +15662,8 @@
       </c>
       <c r="B110" s="44"/>
       <c r="C110" s="46"/>
-      <c r="D110" s="40"/>
-      <c r="E110" s="40"/>
+      <c r="D110" s="42"/>
+      <c r="E110" s="42"/>
       <c r="F110" s="14" t="s">
         <v>267</v>
       </c>
@@ -15807,8 +15742,8 @@
       </c>
       <c r="B111" s="44"/>
       <c r="C111" s="46"/>
-      <c r="D111" s="40"/>
-      <c r="E111" s="40"/>
+      <c r="D111" s="42"/>
+      <c r="E111" s="42"/>
       <c r="F111" s="14" t="s">
         <v>267</v>
       </c>
@@ -15887,8 +15822,8 @@
       </c>
       <c r="B112" s="44"/>
       <c r="C112" s="46"/>
-      <c r="D112" s="40"/>
-      <c r="E112" s="40"/>
+      <c r="D112" s="42"/>
+      <c r="E112" s="42"/>
       <c r="F112" s="14" t="s">
         <v>267</v>
       </c>
@@ -15966,8 +15901,8 @@
       </c>
       <c r="B113" s="44"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="40"/>
-      <c r="E113" s="40"/>
+      <c r="D113" s="42"/>
+      <c r="E113" s="42"/>
       <c r="F113" s="14" t="s">
         <v>267</v>
       </c>
@@ -16044,8 +15979,8 @@
       </c>
       <c r="B114" s="44"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="40"/>
-      <c r="E114" s="40"/>
+      <c r="D114" s="42"/>
+      <c r="E114" s="42"/>
       <c r="F114" s="14" t="s">
         <v>267</v>
       </c>
@@ -16124,8 +16059,8 @@
       </c>
       <c r="B115" s="44"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="40"/>
-      <c r="E115" s="40"/>
+      <c r="D115" s="42"/>
+      <c r="E115" s="42"/>
       <c r="F115" s="14" t="s">
         <v>267</v>
       </c>
@@ -16204,8 +16139,8 @@
       </c>
       <c r="B116" s="44"/>
       <c r="C116" s="46"/>
-      <c r="D116" s="40"/>
-      <c r="E116" s="40"/>
+      <c r="D116" s="42"/>
+      <c r="E116" s="42"/>
       <c r="F116" s="14" t="s">
         <v>267</v>
       </c>
@@ -16285,8 +16220,8 @@
       </c>
       <c r="B117" s="44"/>
       <c r="C117" s="46"/>
-      <c r="D117" s="40"/>
-      <c r="E117" s="40"/>
+      <c r="D117" s="42"/>
+      <c r="E117" s="42"/>
       <c r="F117" s="14" t="s">
         <v>267</v>
       </c>
@@ -16363,8 +16298,8 @@
       </c>
       <c r="B118" s="44"/>
       <c r="C118" s="46"/>
-      <c r="D118" s="40"/>
-      <c r="E118" s="40"/>
+      <c r="D118" s="42"/>
+      <c r="E118" s="42"/>
       <c r="F118" s="14" t="s">
         <v>267</v>
       </c>
@@ -16443,8 +16378,8 @@
       </c>
       <c r="B119" s="44"/>
       <c r="C119" s="46"/>
-      <c r="D119" s="40"/>
-      <c r="E119" s="40"/>
+      <c r="D119" s="42"/>
+      <c r="E119" s="42"/>
       <c r="F119" s="14" t="s">
         <v>267</v>
       </c>
@@ -16525,8 +16460,8 @@
       </c>
       <c r="B120" s="44"/>
       <c r="C120" s="46"/>
-      <c r="D120" s="40"/>
-      <c r="E120" s="40"/>
+      <c r="D120" s="42"/>
+      <c r="E120" s="42"/>
       <c r="F120" s="14" t="s">
         <v>267</v>
       </c>
@@ -16606,8 +16541,8 @@
       </c>
       <c r="B121" s="44"/>
       <c r="C121" s="46"/>
-      <c r="D121" s="40"/>
-      <c r="E121" s="40"/>
+      <c r="D121" s="42"/>
+      <c r="E121" s="42"/>
       <c r="F121" s="14" t="s">
         <v>267</v>
       </c>
@@ -16686,8 +16621,8 @@
       </c>
       <c r="B122" s="44"/>
       <c r="C122" s="46"/>
-      <c r="D122" s="40"/>
-      <c r="E122" s="40"/>
+      <c r="D122" s="42"/>
+      <c r="E122" s="42"/>
       <c r="F122" s="14" t="s">
         <v>267</v>
       </c>
@@ -16768,8 +16703,8 @@
       </c>
       <c r="B123" s="44"/>
       <c r="C123" s="46"/>
-      <c r="D123" s="40"/>
-      <c r="E123" s="40"/>
+      <c r="D123" s="42"/>
+      <c r="E123" s="42"/>
       <c r="F123" s="14" t="s">
         <v>267</v>
       </c>
@@ -16850,8 +16785,8 @@
       </c>
       <c r="B124" s="44"/>
       <c r="C124" s="46"/>
-      <c r="D124" s="40"/>
-      <c r="E124" s="40"/>
+      <c r="D124" s="42"/>
+      <c r="E124" s="42"/>
       <c r="F124" s="14" t="s">
         <v>267</v>
       </c>
@@ -16931,8 +16866,8 @@
       </c>
       <c r="B125" s="44"/>
       <c r="C125" s="46"/>
-      <c r="D125" s="40"/>
-      <c r="E125" s="40"/>
+      <c r="D125" s="42"/>
+      <c r="E125" s="42"/>
       <c r="F125" s="14" t="s">
         <v>267</v>
       </c>
@@ -17013,8 +16948,8 @@
       </c>
       <c r="B126" s="44"/>
       <c r="C126" s="46"/>
-      <c r="D126" s="40"/>
-      <c r="E126" s="40"/>
+      <c r="D126" s="42"/>
+      <c r="E126" s="42"/>
       <c r="F126" s="14" t="s">
         <v>267</v>
       </c>
@@ -17095,8 +17030,8 @@
       </c>
       <c r="B127" s="44"/>
       <c r="C127" s="46"/>
-      <c r="D127" s="40"/>
-      <c r="E127" s="40"/>
+      <c r="D127" s="42"/>
+      <c r="E127" s="42"/>
       <c r="F127" s="14" t="s">
         <v>267</v>
       </c>
@@ -17179,8 +17114,8 @@
       </c>
       <c r="B128" s="44"/>
       <c r="C128" s="46"/>
-      <c r="D128" s="40"/>
-      <c r="E128" s="40"/>
+      <c r="D128" s="42"/>
+      <c r="E128" s="42"/>
       <c r="F128" s="14" t="s">
         <v>267</v>
       </c>
@@ -17262,8 +17197,8 @@
       </c>
       <c r="B129" s="44"/>
       <c r="C129" s="46"/>
-      <c r="D129" s="40"/>
-      <c r="E129" s="40"/>
+      <c r="D129" s="42"/>
+      <c r="E129" s="42"/>
       <c r="F129" s="14" t="s">
         <v>267</v>
       </c>
@@ -17342,8 +17277,8 @@
       </c>
       <c r="B130" s="44"/>
       <c r="C130" s="46"/>
-      <c r="D130" s="40"/>
-      <c r="E130" s="40"/>
+      <c r="D130" s="42"/>
+      <c r="E130" s="42"/>
       <c r="F130" s="14" t="s">
         <v>267</v>
       </c>
@@ -17424,8 +17359,8 @@
       </c>
       <c r="B131" s="44"/>
       <c r="C131" s="46"/>
-      <c r="D131" s="40"/>
-      <c r="E131" s="40"/>
+      <c r="D131" s="42"/>
+      <c r="E131" s="42"/>
       <c r="F131" s="14" t="s">
         <v>267</v>
       </c>
@@ -17504,8 +17439,8 @@
       </c>
       <c r="B132" s="44"/>
       <c r="C132" s="46"/>
-      <c r="D132" s="40"/>
-      <c r="E132" s="40"/>
+      <c r="D132" s="42"/>
+      <c r="E132" s="42"/>
       <c r="F132" s="14" t="s">
         <v>267</v>
       </c>
@@ -17583,8 +17518,8 @@
       </c>
       <c r="B133" s="44"/>
       <c r="C133" s="46"/>
-      <c r="D133" s="40"/>
-      <c r="E133" s="40"/>
+      <c r="D133" s="42"/>
+      <c r="E133" s="42"/>
       <c r="F133" s="14" t="s">
         <v>267</v>
       </c>
@@ -17663,8 +17598,8 @@
       </c>
       <c r="B134" s="44"/>
       <c r="C134" s="46"/>
-      <c r="D134" s="40"/>
-      <c r="E134" s="40"/>
+      <c r="D134" s="42"/>
+      <c r="E134" s="42"/>
       <c r="F134" s="14" t="s">
         <v>267</v>
       </c>
@@ -17741,8 +17676,8 @@
       </c>
       <c r="B135" s="44"/>
       <c r="C135" s="46"/>
-      <c r="D135" s="40"/>
-      <c r="E135" s="40"/>
+      <c r="D135" s="42"/>
+      <c r="E135" s="42"/>
       <c r="F135" s="14" t="s">
         <v>267</v>
       </c>
@@ -17821,8 +17756,8 @@
       </c>
       <c r="B136" s="44"/>
       <c r="C136" s="46"/>
-      <c r="D136" s="40"/>
-      <c r="E136" s="40"/>
+      <c r="D136" s="42"/>
+      <c r="E136" s="42"/>
       <c r="F136" s="14" t="s">
         <v>267</v>
       </c>
@@ -17900,8 +17835,8 @@
       </c>
       <c r="B137" s="44"/>
       <c r="C137" s="46"/>
-      <c r="D137" s="40"/>
-      <c r="E137" s="40"/>
+      <c r="D137" s="42"/>
+      <c r="E137" s="42"/>
       <c r="F137" s="14" t="s">
         <v>267</v>
       </c>
@@ -17980,8 +17915,8 @@
       </c>
       <c r="B138" s="44"/>
       <c r="C138" s="46"/>
-      <c r="D138" s="40"/>
-      <c r="E138" s="40"/>
+      <c r="D138" s="42"/>
+      <c r="E138" s="42"/>
       <c r="F138" s="14" t="s">
         <v>267</v>
       </c>
@@ -18058,8 +17993,8 @@
       </c>
       <c r="B139" s="44"/>
       <c r="C139" s="46"/>
-      <c r="D139" s="40"/>
-      <c r="E139" s="40"/>
+      <c r="D139" s="42"/>
+      <c r="E139" s="42"/>
       <c r="F139" s="14" t="s">
         <v>267</v>
       </c>
@@ -18140,8 +18075,8 @@
       </c>
       <c r="B140" s="44"/>
       <c r="C140" s="46"/>
-      <c r="D140" s="40"/>
-      <c r="E140" s="40"/>
+      <c r="D140" s="42"/>
+      <c r="E140" s="42"/>
       <c r="F140" s="14" t="s">
         <v>267</v>
       </c>
@@ -18219,8 +18154,8 @@
       </c>
       <c r="B141" s="44"/>
       <c r="C141" s="46"/>
-      <c r="D141" s="40"/>
-      <c r="E141" s="40"/>
+      <c r="D141" s="42"/>
+      <c r="E141" s="42"/>
       <c r="F141" s="14" t="s">
         <v>267</v>
       </c>
@@ -18299,8 +18234,8 @@
       </c>
       <c r="B142" s="44"/>
       <c r="C142" s="46"/>
-      <c r="D142" s="40"/>
-      <c r="E142" s="40"/>
+      <c r="D142" s="42"/>
+      <c r="E142" s="42"/>
       <c r="F142" s="14" t="s">
         <v>267</v>
       </c>
@@ -18379,7 +18314,7 @@
       <c r="C143" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="D143" s="40" t="s">
+      <c r="D143" s="42" t="s">
         <v>23</v>
       </c>
       <c r="E143" s="43" t="s">
@@ -18419,7 +18354,7 @@
       </c>
       <c r="B144" s="44"/>
       <c r="C144" s="44"/>
-      <c r="D144" s="40"/>
+      <c r="D144" s="42"/>
       <c r="E144" s="44"/>
       <c r="F144" s="14" t="s">
         <v>268</v>
@@ -18455,7 +18390,7 @@
       </c>
       <c r="B145" s="44"/>
       <c r="C145" s="44"/>
-      <c r="D145" s="40"/>
+      <c r="D145" s="42"/>
       <c r="E145" s="44"/>
       <c r="F145" s="14" t="s">
         <v>268</v>
@@ -18491,7 +18426,7 @@
       </c>
       <c r="B146" s="44"/>
       <c r="C146" s="44"/>
-      <c r="D146" s="40"/>
+      <c r="D146" s="42"/>
       <c r="E146" s="44"/>
       <c r="F146" s="14" t="s">
         <v>268</v>
@@ -18527,7 +18462,7 @@
       </c>
       <c r="B147" s="44"/>
       <c r="C147" s="44"/>
-      <c r="D147" s="40"/>
+      <c r="D147" s="42"/>
       <c r="E147" s="44"/>
       <c r="F147" s="14" t="s">
         <v>268</v>
@@ -18563,7 +18498,7 @@
       </c>
       <c r="B148" s="44"/>
       <c r="C148" s="44"/>
-      <c r="D148" s="40"/>
+      <c r="D148" s="42"/>
       <c r="E148" s="44"/>
       <c r="F148" s="14" t="s">
         <v>268</v>
@@ -18599,7 +18534,7 @@
       </c>
       <c r="B149" s="44"/>
       <c r="C149" s="44"/>
-      <c r="D149" s="40"/>
+      <c r="D149" s="42"/>
       <c r="E149" s="44"/>
       <c r="F149" s="14" t="s">
         <v>268</v>
@@ -18788,7 +18723,7 @@
         <v>151</v>
       </c>
       <c r="B154" s="44"/>
-      <c r="C154" s="41" t="s">
+      <c r="C154" s="47" t="s">
         <v>307</v>
       </c>
       <c r="D154" s="43" t="s">
@@ -18830,7 +18765,7 @@
         <v>152</v>
       </c>
       <c r="B155" s="44"/>
-      <c r="C155" s="42"/>
+      <c r="C155" s="48"/>
       <c r="D155" s="44"/>
       <c r="E155" s="44"/>
       <c r="F155" s="14" t="s">
@@ -18866,7 +18801,7 @@
         <v>153</v>
       </c>
       <c r="B156" s="44"/>
-      <c r="C156" s="42"/>
+      <c r="C156" s="48"/>
       <c r="D156" s="45"/>
       <c r="E156" s="14" t="s">
         <v>310</v>
@@ -18904,11 +18839,11 @@
         <v>154</v>
       </c>
       <c r="B157" s="44"/>
-      <c r="C157" s="42"/>
-      <c r="D157" s="40" t="s">
+      <c r="C157" s="48"/>
+      <c r="D157" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="E157" s="41" t="s">
+      <c r="E157" s="47" t="s">
         <v>280</v>
       </c>
       <c r="F157" s="14" t="s">
@@ -18944,9 +18879,9 @@
         <v>155</v>
       </c>
       <c r="B158" s="44"/>
-      <c r="C158" s="42"/>
-      <c r="D158" s="40"/>
-      <c r="E158" s="42"/>
+      <c r="C158" s="48"/>
+      <c r="D158" s="42"/>
+      <c r="E158" s="48"/>
       <c r="F158" s="14" t="s">
         <v>267</v>
       </c>
@@ -18980,9 +18915,9 @@
         <v>156</v>
       </c>
       <c r="B159" s="44"/>
-      <c r="C159" s="42"/>
-      <c r="D159" s="40"/>
-      <c r="E159" s="42"/>
+      <c r="C159" s="48"/>
+      <c r="D159" s="42"/>
+      <c r="E159" s="48"/>
       <c r="F159" s="14" t="s">
         <v>267</v>
       </c>
@@ -19016,8 +18951,8 @@
         <v>157</v>
       </c>
       <c r="B160" s="44"/>
-      <c r="C160" s="42"/>
-      <c r="D160" s="40"/>
+      <c r="C160" s="48"/>
+      <c r="D160" s="42"/>
       <c r="E160" s="44"/>
       <c r="F160" s="14" t="s">
         <v>267</v>
@@ -19052,8 +18987,8 @@
         <v>158</v>
       </c>
       <c r="B161" s="44"/>
-      <c r="C161" s="42"/>
-      <c r="D161" s="40"/>
+      <c r="C161" s="48"/>
+      <c r="D161" s="42"/>
       <c r="E161" s="44"/>
       <c r="F161" s="14" t="s">
         <v>267</v>
@@ -19088,8 +19023,8 @@
         <v>159</v>
       </c>
       <c r="B162" s="44"/>
-      <c r="C162" s="42"/>
-      <c r="D162" s="40"/>
+      <c r="C162" s="48"/>
+      <c r="D162" s="42"/>
       <c r="E162" s="44"/>
       <c r="F162" s="14" t="s">
         <v>267</v>
@@ -19124,8 +19059,8 @@
         <v>160</v>
       </c>
       <c r="B163" s="44"/>
-      <c r="C163" s="42"/>
-      <c r="D163" s="40"/>
+      <c r="C163" s="48"/>
+      <c r="D163" s="42"/>
       <c r="E163" s="44"/>
       <c r="F163" s="14" t="s">
         <v>267</v>
@@ -19160,8 +19095,8 @@
         <v>161</v>
       </c>
       <c r="B164" s="44"/>
-      <c r="C164" s="42"/>
-      <c r="D164" s="40"/>
+      <c r="C164" s="48"/>
+      <c r="D164" s="42"/>
       <c r="E164" s="44"/>
       <c r="F164" s="14" t="s">
         <v>267</v>
@@ -19196,8 +19131,8 @@
         <v>162</v>
       </c>
       <c r="B165" s="44"/>
-      <c r="C165" s="42"/>
-      <c r="D165" s="40"/>
+      <c r="C165" s="48"/>
+      <c r="D165" s="42"/>
       <c r="E165" s="44"/>
       <c r="F165" s="14" t="s">
         <v>267</v>
@@ -19232,8 +19167,8 @@
         <v>163</v>
       </c>
       <c r="B166" s="44"/>
-      <c r="C166" s="42"/>
-      <c r="D166" s="40"/>
+      <c r="C166" s="48"/>
+      <c r="D166" s="42"/>
       <c r="E166" s="44"/>
       <c r="F166" s="14" t="s">
         <v>267</v>
@@ -19268,8 +19203,8 @@
         <v>164</v>
       </c>
       <c r="B167" s="44"/>
-      <c r="C167" s="42"/>
-      <c r="D167" s="40"/>
+      <c r="C167" s="48"/>
+      <c r="D167" s="42"/>
       <c r="E167" s="44"/>
       <c r="F167" s="14" t="s">
         <v>267</v>
@@ -19305,8 +19240,8 @@
         <v>165</v>
       </c>
       <c r="B168" s="44"/>
-      <c r="C168" s="42"/>
-      <c r="D168" s="40"/>
+      <c r="C168" s="48"/>
+      <c r="D168" s="42"/>
       <c r="E168" s="44"/>
       <c r="F168" s="14" t="s">
         <v>267</v>
@@ -19342,8 +19277,8 @@
         <v>166</v>
       </c>
       <c r="B169" s="44"/>
-      <c r="C169" s="42"/>
-      <c r="D169" s="40"/>
+      <c r="C169" s="48"/>
+      <c r="D169" s="42"/>
       <c r="E169" s="44"/>
       <c r="F169" s="14" t="s">
         <v>267</v>
@@ -19417,8 +19352,8 @@
         <v>167</v>
       </c>
       <c r="B170" s="44"/>
-      <c r="C170" s="42"/>
-      <c r="D170" s="40"/>
+      <c r="C170" s="48"/>
+      <c r="D170" s="42"/>
       <c r="E170" s="44"/>
       <c r="F170" s="14" t="s">
         <v>267</v>
@@ -19454,8 +19389,8 @@
         <v>168</v>
       </c>
       <c r="B171" s="44"/>
-      <c r="C171" s="42"/>
-      <c r="D171" s="40"/>
+      <c r="C171" s="48"/>
+      <c r="D171" s="42"/>
       <c r="E171" s="44"/>
       <c r="F171" s="14" t="s">
         <v>267</v>
@@ -19491,8 +19426,8 @@
         <v>169</v>
       </c>
       <c r="B172" s="44"/>
-      <c r="C172" s="42"/>
-      <c r="D172" s="40"/>
+      <c r="C172" s="48"/>
+      <c r="D172" s="42"/>
       <c r="E172" s="44"/>
       <c r="F172" s="14" t="s">
         <v>267</v>
@@ -19528,8 +19463,8 @@
         <v>170</v>
       </c>
       <c r="B173" s="44"/>
-      <c r="C173" s="42"/>
-      <c r="D173" s="40"/>
+      <c r="C173" s="48"/>
+      <c r="D173" s="42"/>
       <c r="E173" s="44"/>
       <c r="F173" s="14" t="s">
         <v>267</v>
@@ -19565,8 +19500,8 @@
         <v>171</v>
       </c>
       <c r="B174" s="44"/>
-      <c r="C174" s="42"/>
-      <c r="D174" s="40"/>
+      <c r="C174" s="48"/>
+      <c r="D174" s="42"/>
       <c r="E174" s="44"/>
       <c r="F174" s="14" t="s">
         <v>267</v>
@@ -19602,8 +19537,8 @@
         <v>172</v>
       </c>
       <c r="B175" s="44"/>
-      <c r="C175" s="42"/>
-      <c r="D175" s="40"/>
+      <c r="C175" s="48"/>
+      <c r="D175" s="42"/>
       <c r="E175" s="44"/>
       <c r="F175" s="14" t="s">
         <v>267</v>
@@ -19639,8 +19574,8 @@
         <v>173</v>
       </c>
       <c r="B176" s="44"/>
-      <c r="C176" s="42"/>
-      <c r="D176" s="40"/>
+      <c r="C176" s="48"/>
+      <c r="D176" s="42"/>
       <c r="E176" s="44"/>
       <c r="F176" s="14" t="s">
         <v>267</v>
@@ -19675,16 +19610,16 @@
       <c r="A177" s="14">
         <v>174</v>
       </c>
-      <c r="B177" s="40" t="s">
+      <c r="B177" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="C177" s="40" t="s">
+      <c r="C177" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="D177" s="40" t="s">
+      <c r="D177" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="E177" s="40" t="s">
+      <c r="E177" s="42" t="s">
         <v>18</v>
       </c>
       <c r="F177" s="14" t="s">
@@ -19721,10 +19656,10 @@
       <c r="A178" s="14">
         <v>175</v>
       </c>
-      <c r="B178" s="40"/>
-      <c r="C178" s="40"/>
-      <c r="D178" s="40"/>
-      <c r="E178" s="40"/>
+      <c r="B178" s="42"/>
+      <c r="C178" s="42"/>
+      <c r="D178" s="42"/>
+      <c r="E178" s="42"/>
       <c r="F178" s="14" t="s">
         <v>268</v>
       </c>
@@ -19759,10 +19694,10 @@
       <c r="A179" s="14">
         <v>176</v>
       </c>
-      <c r="B179" s="40"/>
-      <c r="C179" s="40"/>
-      <c r="D179" s="40"/>
-      <c r="E179" s="40"/>
+      <c r="B179" s="42"/>
+      <c r="C179" s="42"/>
+      <c r="D179" s="42"/>
+      <c r="E179" s="42"/>
       <c r="F179" s="14" t="s">
         <v>268</v>
       </c>
@@ -19797,10 +19732,10 @@
       <c r="A180" s="14">
         <v>177</v>
       </c>
-      <c r="B180" s="40"/>
-      <c r="C180" s="40"/>
-      <c r="D180" s="40"/>
-      <c r="E180" s="40"/>
+      <c r="B180" s="42"/>
+      <c r="C180" s="42"/>
+      <c r="D180" s="42"/>
+      <c r="E180" s="42"/>
       <c r="F180" s="14" t="s">
         <v>268</v>
       </c>
@@ -19835,10 +19770,10 @@
       <c r="A181" s="14">
         <v>178</v>
       </c>
-      <c r="B181" s="40"/>
-      <c r="C181" s="40"/>
-      <c r="D181" s="40"/>
-      <c r="E181" s="40"/>
+      <c r="B181" s="42"/>
+      <c r="C181" s="42"/>
+      <c r="D181" s="42"/>
+      <c r="E181" s="42"/>
       <c r="F181" s="14" t="s">
         <v>268</v>
       </c>
@@ -19873,12 +19808,12 @@
       <c r="A182" s="14">
         <v>179</v>
       </c>
-      <c r="B182" s="40"/>
-      <c r="C182" s="40"/>
-      <c r="D182" s="40" t="s">
+      <c r="B182" s="42"/>
+      <c r="C182" s="42"/>
+      <c r="D182" s="42" t="s">
         <v>288</v>
       </c>
-      <c r="E182" s="40"/>
+      <c r="E182" s="42"/>
       <c r="F182" s="14" t="s">
         <v>268</v>
       </c>
@@ -19913,10 +19848,10 @@
       <c r="A183" s="14">
         <v>180</v>
       </c>
-      <c r="B183" s="40"/>
-      <c r="C183" s="40"/>
-      <c r="D183" s="40"/>
-      <c r="E183" s="40"/>
+      <c r="B183" s="42"/>
+      <c r="C183" s="42"/>
+      <c r="D183" s="42"/>
+      <c r="E183" s="42"/>
       <c r="F183" s="14" t="s">
         <v>268</v>
       </c>
@@ -19951,10 +19886,10 @@
       <c r="A184" s="14">
         <v>181</v>
       </c>
-      <c r="B184" s="40"/>
-      <c r="C184" s="40"/>
-      <c r="D184" s="40"/>
-      <c r="E184" s="40"/>
+      <c r="B184" s="42"/>
+      <c r="C184" s="42"/>
+      <c r="D184" s="42"/>
+      <c r="E184" s="42"/>
       <c r="F184" s="14" t="s">
         <v>268</v>
       </c>
@@ -19989,9 +19924,9 @@
       <c r="A185" s="14">
         <v>182</v>
       </c>
-      <c r="B185" s="40"/>
-      <c r="C185" s="40"/>
-      <c r="D185" s="40"/>
+      <c r="B185" s="42"/>
+      <c r="C185" s="42"/>
+      <c r="D185" s="42"/>
       <c r="E185" s="14" t="s">
         <v>329</v>
       </c>
@@ -20033,6 +19968,20 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="C154:C176"/>
+    <mergeCell ref="D154:D156"/>
+    <mergeCell ref="E154:E155"/>
+    <mergeCell ref="D157:D176"/>
+    <mergeCell ref="E157:E176"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="D182:D185"/>
+    <mergeCell ref="D177:D181"/>
+    <mergeCell ref="E177:E184"/>
+    <mergeCell ref="B177:B185"/>
+    <mergeCell ref="C177:C185"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="E4:E142"/>
@@ -20043,146 +19992,97 @@
     <mergeCell ref="D150:D153"/>
     <mergeCell ref="E143:E152"/>
     <mergeCell ref="C4:C142"/>
-    <mergeCell ref="D182:D185"/>
-    <mergeCell ref="D177:D181"/>
-    <mergeCell ref="E177:E184"/>
-    <mergeCell ref="B177:B185"/>
-    <mergeCell ref="C177:C185"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="C154:C176"/>
-    <mergeCell ref="D154:D156"/>
-    <mergeCell ref="E154:E155"/>
-    <mergeCell ref="D157:D176"/>
-    <mergeCell ref="E157:E176"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="M4:M153">
-    <cfRule type="containsText" dxfId="31" priority="38" operator="containsText" text="非該当">
-      <formula>NOT(ISERROR(SEARCH("非該当",M4)))</formula>
+  <conditionalFormatting sqref="F4:F185">
+    <cfRule type="cellIs" dxfId="22" priority="43" operator="equal">
+      <formula>"中"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="45" operator="containsText" text="修正中">
-      <formula>NOT(ISERROR(SEARCH("修正中",M4)))</formula>
+    <cfRule type="cellIs" dxfId="21" priority="44" operator="equal">
+      <formula>"高"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="46" operator="containsText" text="テスト待ち">
-      <formula>NOT(ISERROR(SEARCH("テスト待ち",M4)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="47" operator="containsText" text="保留">
-      <formula>NOT(ISERROR(SEARCH("保留",M4)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="48" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",M4)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="50" stopIfTrue="1" operator="equal">
-      <formula>"OK"</formula>
+    <cfRule type="cellIs" dxfId="20" priority="42" operator="equal">
+      <formula>"低"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F185">
-    <cfRule type="cellIs" dxfId="25" priority="42" operator="equal">
-      <formula>"低"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="43" operator="equal">
-      <formula>"中"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="44" operator="equal">
-      <formula>"高"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G91:G143 G4:I90 H91:I153">
-    <cfRule type="cellIs" dxfId="22" priority="41" operator="equal">
+  <conditionalFormatting sqref="G150:G156">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
       <formula>"なし"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G153 G177">
-    <cfRule type="cellIs" dxfId="21" priority="40" operator="equal">
+  <conditionalFormatting sqref="G177">
+    <cfRule type="cellIs" dxfId="18" priority="40" operator="equal">
+      <formula>"なし"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G182:G185">
+    <cfRule type="cellIs" dxfId="17" priority="22" operator="equal">
+      <formula>"なし"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:I90 G91:G143">
+    <cfRule type="cellIs" dxfId="16" priority="41" operator="equal">
+      <formula>"なし"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G157:I176">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
       <formula>"なし"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H177:H185">
-    <cfRule type="cellIs" dxfId="20" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="32" operator="equal">
       <formula>"なし"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G150:G152">
-    <cfRule type="cellIs" dxfId="19" priority="31" operator="equal">
-      <formula>"なし"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M182:M185">
-    <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="非該当">
-      <formula>NOT(ISERROR(SEARCH("非該当",M182)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="26" operator="containsText" text="修正中">
-      <formula>NOT(ISERROR(SEARCH("修正中",M182)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="27" operator="containsText" text="テスト待ち">
-      <formula>NOT(ISERROR(SEARCH("テスト待ち",M182)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="28" operator="containsText" text="保留">
-      <formula>NOT(ISERROR(SEARCH("保留",M182)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="29" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",M182)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="30" stopIfTrue="1" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G185">
-    <cfRule type="cellIs" dxfId="12" priority="24" operator="equal">
-      <formula>"なし"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G182:G184">
-    <cfRule type="cellIs" dxfId="11" priority="22" operator="equal">
-      <formula>"なし"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M154:M176">
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="非該当">
-      <formula>NOT(ISERROR(SEARCH("非該当",M154)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="修正中">
-      <formula>NOT(ISERROR(SEARCH("修正中",M154)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="テスト待ち">
-      <formula>NOT(ISERROR(SEARCH("テスト待ち",M154)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="保留">
-      <formula>NOT(ISERROR(SEARCH("保留",M154)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="10" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",M154)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="11" stopIfTrue="1" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G157:I176">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
-      <formula>"なし"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G154:G156">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
-      <formula>"なし"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H154:I155">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"なし"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H156:I156">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+  <conditionalFormatting sqref="H91:I156">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"なし"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4:L185">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"-"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:M176">
+    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="NG">
+      <formula>NOT(ISERROR(SEARCH("NG",M4)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="11" stopIfTrue="1" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="テスト待ち">
+      <formula>NOT(ISERROR(SEARCH("テスト待ち",M4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="7" operator="containsText" text="修正中">
+      <formula>NOT(ISERROR(SEARCH("修正中",M4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="非該当">
+      <formula>NOT(ISERROR(SEARCH("非該当",M4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="保留">
+      <formula>NOT(ISERROR(SEARCH("保留",M4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M182:M185">
+    <cfRule type="containsText" dxfId="5" priority="29" operator="containsText" text="NG">
+      <formula>NOT(ISERROR(SEARCH("NG",M182)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="30" stopIfTrue="1" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="23" operator="containsText" text="非該当">
+      <formula>NOT(ISERROR(SEARCH("非該当",M182)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="28" operator="containsText" text="保留">
+      <formula>NOT(ISERROR(SEARCH("保留",M182)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="26" operator="containsText" text="修正中">
+      <formula>NOT(ISERROR(SEARCH("修正中",M182)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="27" operator="containsText" text="テスト待ち">
+      <formula>NOT(ISERROR(SEARCH("テスト待ち",M182)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -20201,17 +20101,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45AA8221-A32C-8E49-B3C0-C2B2672E527B}">
-  <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02BDD09C-DD5A-4F4A-A722-D4CC505A244D}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:E56"/>
@@ -20602,7 +20491,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4325A6B3-002D-084B-917F-017C1C7A0D6E}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:B9"/>
